--- a/diseases/d037/2000-2004.xlsx
+++ b/diseases/d037/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -1688,9 +1685,6 @@
       <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.2226741517840542</v>
       </c>
@@ -2232,9 +2226,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -3007,9 +2998,6 @@
       <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -3551,9 +3539,6 @@
       <c r="O17" t="n">
         <v>5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -4326,9 +4311,6 @@
       <c r="O21" t="n">
         <v>3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -4870,9 +4852,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -5645,9 +5624,6 @@
       <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -6189,9 +6165,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6964,9 +6937,6 @@
       <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -7508,9 +7478,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -8283,9 +8250,6 @@
       <c r="O42" t="n">
         <v>7</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -8827,9 +8791,6 @@
       <c r="O45" t="n">
         <v>7</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1352343026058781</v>
       </c>
@@ -9602,9 +9563,6 @@
       <c r="O49" t="n">
         <v>6</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -10146,9 +10104,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -10921,9 +10876,6 @@
       <c r="O56" t="n">
         <v>9</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -11465,9 +11417,6 @@
       <c r="O59" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -12240,9 +12189,6 @@
       <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -12784,9 +12730,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -13559,9 +13502,6 @@
       <c r="O70" t="n">
         <v>8</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -14103,9 +14043,6 @@
       <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -14878,9 +14815,6 @@
       <c r="O77" t="n">
         <v>8</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -15422,9 +15356,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -16197,9 +16128,6 @@
       <c r="O84" t="n">
         <v>6</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -16741,9 +16669,6 @@
       <c r="O87" t="n">
         <v>4</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -17516,9 +17441,6 @@
       <c r="O91" t="n">
         <v>14</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.02975971074241381</v>
       </c>
@@ -17664,9 +17586,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -18208,9 +18127,6 @@
       <c r="O95" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -18983,9 +18899,6 @@
       <c r="O99" t="n">
         <v>19</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.04038817886470444</v>
       </c>
@@ -19131,9 +19044,6 @@
       <c r="O100" t="n">
         <v>7</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -19675,9 +19585,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -20450,9 +20357,6 @@
       <c r="O107" t="n">
         <v>34</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.07227358323157637</v>
       </c>
@@ -20598,9 +20502,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -21142,9 +21043,6 @@
       <c r="O111" t="n">
         <v>3</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -21917,9 +21815,6 @@
       <c r="O115" t="n">
         <v>45</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0956562131006158</v>
       </c>
@@ -22065,9 +21960,6 @@
       <c r="O116" t="n">
         <v>12</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -22609,9 +22501,6 @@
       <c r="O119" t="n">
         <v>5</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -23384,9 +23273,6 @@
       <c r="O123" t="n">
         <v>176</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.3741220779046307</v>
       </c>
@@ -23532,9 +23418,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -24076,9 +23959,6 @@
       <c r="O127" t="n">
         <v>9</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.1734782249168317</v>
       </c>
@@ -24851,9 +24731,6 @@
       <c r="O131" t="n">
         <v>369</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.7843809474250495</v>
       </c>
@@ -24999,9 +24876,6 @@
       <c r="O132" t="n">
         <v>6</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -25543,9 +25417,6 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -26318,9 +26189,6 @@
       <c r="O139" t="n">
         <v>681</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>1.447597358255986</v>
       </c>
@@ -26466,9 +26334,6 @@
       <c r="O140" t="n">
         <v>5</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -27010,9 +26875,6 @@
       <c r="O143" t="n">
         <v>6</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -27785,9 +27647,6 @@
       <c r="O147" t="n">
         <v>624</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>1.326432821661872</v>
       </c>
@@ -27933,9 +27792,6 @@
       <c r="O148" t="n">
         <v>20</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.4430996861303373</v>
       </c>
@@ -28477,9 +28333,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -29252,9 +29105,6 @@
       <c r="O155" t="n">
         <v>378</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.8035121900451727</v>
       </c>
@@ -29400,9 +29250,6 @@
       <c r="O156" t="n">
         <v>8</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.1772398744521349</v>
       </c>
@@ -29944,9 +29791,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -30719,9 +30563,6 @@
       <c r="O163" t="n">
         <v>173</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.3677449970312563</v>
       </c>
@@ -30867,9 +30708,6 @@
       <c r="O164" t="n">
         <v>11</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -31411,9 +31249,6 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -32186,9 +32021,6 @@
       <c r="O171" t="n">
         <v>30</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.06377080873374386</v>
       </c>
@@ -32334,9 +32166,6 @@
       <c r="O172" t="n">
         <v>5</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -32878,9 +32707,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -33653,9 +33479,6 @@
       <c r="O179" t="n">
         <v>13</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.02763401711795567</v>
       </c>
@@ -33801,9 +33624,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -34345,9 +34165,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -35120,9 +34937,6 @@
       <c r="O187" t="n">
         <v>11</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.02325624638200197</v>
       </c>
@@ -35268,9 +35082,6 @@
       <c r="O188" t="n">
         <v>6</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -35812,9 +35623,6 @@
       <c r="O191" t="n">
         <v>4</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -36587,9 +36395,6 @@
       <c r="O195" t="n">
         <v>4</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -36735,9 +36540,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -37279,9 +37081,6 @@
       <c r="O199" t="n">
         <v>4</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -38054,9 +37853,6 @@
       <c r="O203" t="n">
         <v>5</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -38202,9 +37998,6 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -38746,9 +38539,6 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -39521,9 +39311,6 @@
       <c r="O211" t="n">
         <v>34</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.07188294336255154</v>
       </c>
@@ -39669,9 +39456,6 @@
       <c r="O212" t="n">
         <v>5</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -40213,9 +39997,6 @@
       <c r="O215" t="n">
         <v>2</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -40988,9 +40769,6 @@
       <c r="O219" t="n">
         <v>102</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.2156488300876546</v>
       </c>
@@ -41136,9 +40914,6 @@
       <c r="O220" t="n">
         <v>9</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -41680,9 +41455,6 @@
       <c r="O223" t="n">
         <v>2</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -42455,9 +42227,6 @@
       <c r="O227" t="n">
         <v>192</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.4059272095767615</v>
       </c>
@@ -42603,9 +42372,6 @@
       <c r="O228" t="n">
         <v>3</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -43147,9 +42913,6 @@
       <c r="O231" t="n">
         <v>4</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -43922,9 +43685,6 @@
       <c r="O235" t="n">
         <v>407</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.8604811161340727</v>
       </c>
@@ -44070,9 +43830,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -44614,9 +44371,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -45389,9 +45143,6 @@
       <c r="O243" t="n">
         <v>561</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>1.1860685654821</v>
       </c>
@@ -45537,9 +45288,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -46081,9 +45829,6 @@
       <c r="O247" t="n">
         <v>2</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -46856,9 +46601,6 @@
       <c r="O251" t="n">
         <v>297</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.6279186523140531</v>
       </c>
@@ -47004,9 +46746,6 @@
       <c r="O252" t="n">
         <v>11</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.2423967841439008</v>
       </c>
@@ -47548,9 +47287,6 @@
       <c r="O255" t="n">
         <v>3</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -48323,9 +48059,6 @@
       <c r="O259" t="n">
         <v>145</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.3065596113991168</v>
       </c>
@@ -48471,9 +48204,6 @@
       <c r="O260" t="n">
         <v>7</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -49015,9 +48745,6 @@
       <c r="O263" t="n">
         <v>2</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -49790,9 +49517,6 @@
       <c r="O267" t="n">
         <v>36</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.0761113517956428</v>
       </c>
@@ -49938,9 +49662,6 @@
       <c r="O268" t="n">
         <v>2</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -50482,9 +50203,6 @@
       <c r="O271" t="n">
         <v>7</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -51257,9 +50975,6 @@
       <c r="O275" t="n">
         <v>5</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -51405,9 +51120,6 @@
       <c r="O276" t="n">
         <v>1</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -51949,9 +51661,6 @@
       <c r="O279" t="n">
         <v>2</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -52724,9 +52433,6 @@
       <c r="O283" t="n">
         <v>10</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.02104635732751713</v>
       </c>
@@ -52872,9 +52578,6 @@
       <c r="O284" t="n">
         <v>8</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -53416,9 +53119,6 @@
       <c r="O287" t="n">
         <v>1</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -54191,9 +53891,6 @@
       <c r="O291" t="n">
         <v>8</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.01683708586201371</v>
       </c>
@@ -54339,9 +54036,6 @@
       <c r="O292" t="n">
         <v>4</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -55031,9 +54725,6 @@
       <c r="O296" t="n">
         <v>2</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -55806,9 +55497,6 @@
       <c r="O300" t="n">
         <v>9</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -55954,9 +55642,6 @@
       <c r="O301" t="n">
         <v>2</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -56646,9 +56331,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -57421,9 +57103,6 @@
       <c r="O309" t="n">
         <v>25</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.05261589331879283</v>
       </c>
@@ -57569,9 +57248,6 @@
       <c r="O310" t="n">
         <v>5</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -58261,9 +57937,6 @@
       <c r="O314" t="n">
         <v>3</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -59036,9 +58709,6 @@
       <c r="O318" t="n">
         <v>73</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.1536384084908751</v>
       </c>
@@ -59184,9 +58854,6 @@
       <c r="O319" t="n">
         <v>2</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -59876,9 +59543,6 @@
       <c r="O323" t="n">
         <v>1</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -60651,9 +60315,6 @@
       <c r="O327" t="n">
         <v>176</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.3704158889643015</v>
       </c>
@@ -60799,9 +60460,6 @@
       <c r="O328" t="n">
         <v>3</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -61491,9 +61149,6 @@
       <c r="O332" t="n">
         <v>1</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -62266,9 +61921,6 @@
       <c r="O336" t="n">
         <v>275</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.5787748265067211</v>
       </c>
@@ -62414,9 +62066,6 @@
       <c r="O337" t="n">
         <v>7</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -63106,9 +62755,6 @@
       <c r="O341" t="n">
         <v>4</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -63881,9 +63527,6 @@
       <c r="O345" t="n">
         <v>295</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.6208675411617554</v>
       </c>
@@ -64029,9 +63672,6 @@
       <c r="O346" t="n">
         <v>4</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -64721,9 +64361,6 @@
       <c r="O350" t="n">
         <v>2</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -65496,9 +65133,6 @@
       <c r="O354" t="n">
         <v>186</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.3914622462918186</v>
       </c>
@@ -65644,9 +65278,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -66336,9 +65967,6 @@
       <c r="O359" t="n">
         <v>3</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -67111,9 +66739,6 @@
       <c r="O363" t="n">
         <v>85</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.1788940372838956</v>
       </c>
@@ -67259,9 +66884,6 @@
       <c r="O364" t="n">
         <v>5</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -67951,9 +67573,6 @@
       <c r="O368" t="n">
         <v>2</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -68726,9 +68345,6 @@
       <c r="O372" t="n">
         <v>22</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.04630198612053769</v>
       </c>
@@ -68874,9 +68490,6 @@
       <c r="O373" t="n">
         <v>6</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -69566,9 +69179,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -70341,9 +69951,6 @@
       <c r="O381" t="n">
         <v>7</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.01473245012926199</v>
       </c>
@@ -70489,9 +70096,6 @@
       <c r="O382" t="n">
         <v>8</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -71329,9 +70933,6 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
@@ -72104,9 +71705,6 @@
       <c r="O391" t="n">
         <v>6</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -72252,9 +71850,6 @@
       <c r="O392" t="n">
         <v>11</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.2395604718687949</v>
       </c>
@@ -73092,9 +72687,6 @@
       <c r="O397" t="n">
         <v>1</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -73867,9 +73459,6 @@
       <c r="O401" t="n">
         <v>7</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.01467595219753043</v>
       </c>
@@ -74015,9 +73604,6 @@
       <c r="O402" t="n">
         <v>1</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -74855,9 +74441,6 @@
       <c r="O407" t="n">
         <v>2</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -75630,9 +75213,6 @@
       <c r="O411" t="n">
         <v>4</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -75778,9 +75358,6 @@
       <c r="O412" t="n">
         <v>2</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -76618,9 +76195,6 @@
       <c r="O417" t="n">
         <v>3</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -77393,9 +76967,6 @@
       <c r="O421" t="n">
         <v>19</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.03983472739329689</v>
       </c>
@@ -77541,9 +77112,6 @@
       <c r="O422" t="n">
         <v>3</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -78381,9 +77949,6 @@
       <c r="O427" t="n">
         <v>3</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -79156,9 +78721,6 @@
       <c r="O431" t="n">
         <v>42</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0.0880557131851826</v>
       </c>
@@ -79304,9 +78866,6 @@
       <c r="O432" t="n">
         <v>2</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -79996,9 +79555,6 @@
       <c r="O436" t="n">
         <v>2</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -80771,9 +80327,6 @@
       <c r="O440" t="n">
         <v>141</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0.2956156085502559</v>
       </c>
@@ -80919,9 +80472,6 @@
       <c r="O441" t="n">
         <v>1</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -81759,9 +81309,6 @@
       <c r="O446" t="n">
         <v>3</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -82534,9 +82081,6 @@
       <c r="O450" t="n">
         <v>211</v>
       </c>
-      <c r="Q450" t="n">
-        <v>0</v>
-      </c>
       <c r="R450" t="n">
         <v>0.4423751305255602</v>
       </c>
@@ -82682,9 +82226,6 @@
       <c r="O451" t="n">
         <v>14</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0.3048951460148299</v>
       </c>
@@ -83522,9 +83063,6 @@
       <c r="O456" t="n">
         <v>2</v>
       </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
       <c r="R456" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -84297,9 +83835,6 @@
       <c r="O460" t="n">
         <v>214</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0.4486648243245018</v>
       </c>
@@ -84445,9 +83980,6 @@
       <c r="O461" t="n">
         <v>6</v>
       </c>
-      <c r="Q461" t="n">
-        <v>0</v>
-      </c>
       <c r="R461" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -85285,9 +84817,6 @@
       <c r="O466" t="n">
         <v>1</v>
       </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
       <c r="R466" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -86060,9 +85589,6 @@
       <c r="O470" t="n">
         <v>126</v>
       </c>
-      <c r="Q470" t="n">
-        <v>0</v>
-      </c>
       <c r="R470" t="n">
         <v>0.2641671395555478</v>
       </c>
@@ -86208,9 +85734,6 @@
       <c r="O471" t="n">
         <v>5</v>
       </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
       <c r="R471" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -86900,9 +86423,6 @@
       <c r="O475" t="n">
         <v>4</v>
       </c>
-      <c r="Q475" t="n">
-        <v>0</v>
-      </c>
       <c r="R475" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -87675,9 +87195,6 @@
       <c r="O479" t="n">
         <v>76</v>
       </c>
-      <c r="Q479" t="n">
-        <v>0</v>
-      </c>
       <c r="R479" t="n">
         <v>0.1593389095731876</v>
       </c>
@@ -87823,9 +87340,6 @@
       <c r="O480" t="n">
         <v>6</v>
       </c>
-      <c r="Q480" t="n">
-        <v>0</v>
-      </c>
       <c r="R480" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -88663,9 +88177,6 @@
       <c r="O485" t="n">
         <v>3</v>
       </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
       <c r="R485" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -89438,9 +88949,6 @@
       <c r="O489" t="n">
         <v>13</v>
       </c>
-      <c r="Q489" t="n">
-        <v>0</v>
-      </c>
       <c r="R489" t="n">
         <v>0.02725533979541367</v>
       </c>
@@ -89586,9 +89094,6 @@
       <c r="O490" t="n">
         <v>4</v>
       </c>
-      <c r="Q490" t="n">
-        <v>0</v>
-      </c>
       <c r="R490" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -90426,9 +89931,6 @@
       <c r="O495" t="n">
         <v>3</v>
       </c>
-      <c r="Q495" t="n">
-        <v>0</v>
-      </c>
       <c r="R495" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -91201,9 +90703,6 @@
       <c r="O499" t="n">
         <v>5</v>
       </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
       <c r="R499" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -91348,9 +90847,6 @@
       </c>
       <c r="O500" t="n">
         <v>6</v>
-      </c>
-      <c r="Q500" t="n">
-        <v>0</v>
       </c>
       <c r="R500" t="n">
         <v>0.1306693482920699</v>
